--- a/UMA_96_well_plate_template.xlsx
+++ b/UMA_96_well_plate_template.xlsx
@@ -1673,7 +1673,7 @@
     <row r="24" ht="135" customHeight="1">
       <c r="B24" s="75" t="inlineStr">
         <is>
-          <t>uma_report: save exactly one filled .xlsx in &lt;images&gt;/uma_assay/Combined_Results_.../. uma_functional_report: save it in &lt;images&gt;/uma_functional_assay/Cell_Analysis_.../. Both commands select the latest finalized run, including PARTIAL. uma_survival_report: set plate_template to this workbook in your survival JSON. Keep Plate Map as the first worksheet. Each workbook describes one plate.</t>
+          <t>uma_report and uma_functional_report: keep a filled UMA*.xlsx directly beside the original images in each JSON folder. All folders are checked before reports start. One map is automatic; several maps offer a per-folder choice in a terminal. Missing or invalid maps offer retry, skip or cancel. With --non-interactive, problematic folders are logged and skipped. Reports archive the selected map. Collection does not copy it. uma_survival_report: keep the explicit plate_template path in your survival JSON for one map shared by all days. Keep Plate Map as the first worksheet.</t>
         </is>
       </c>
     </row>
